--- a/data/seed/portfolio/L-2024-6720/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6720/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -541,76 +541,76 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6643000</v>
+        <v>37978000</v>
       </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №12/26 от 01.07.2026, НДС 12%</t>
+          <t>Оплата за сырье по договору №125/26 от 01.07.2026,НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>38157000</v>
+        <v>6822000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>4981000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>15236000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Shahrisabz Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>227572578</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000534680922001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9406</t>
+          <t>Оплата по счет-фактуре №3662 за поставленный товар</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>33176000</v>
+        <v>22058000</v>
       </c>
     </row>
     <row r="10">
@@ -622,35 +622,35 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>32475000</v>
+        <v>2380000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bunyodkor Agro MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>268478422</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000356379989001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9510 06.07.2026, QQS bilan</t>
+          <t>Shartnoma №168/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>65651000</v>
+        <v>24438000</v>
       </c>
     </row>
     <row r="11">
@@ -660,63 +660,58 @@
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>6855000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>12836000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bunyodkor Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>268478422</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000356379989001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №235/26, НДС 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>72506000</v>
+        <v>11602000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>7689000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>22928000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,112 +721,117 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №80/26 от 06.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №158/26, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>64817000</v>
+        <v>34530000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>12836000</v>
+        <v>1828000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bog'ishamol Qurilish AJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>377824637</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000662075680001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно рестру №982</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>51981000</v>
+        <v>32702000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>5720000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>6828000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7246 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №284/26</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>57701000</v>
+        <v>25874000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>1828000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>13154000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>241477296</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000275361176001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -841,37 +841,37 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №90/21</t>
+          <t>Оплата за продукцию по договору №250/26, НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>55873000</v>
+        <v>39028000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>3464000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>1731000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -881,51 +881,51 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №107/26 ОТ 08.07.2026, НДС 12%</t>
+          <t>Shartnoma №294/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>52409000</v>
+        <v>40759000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>9138000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>2177000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №36/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4641 10.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>43271000</v>
+        <v>42936000</v>
       </c>
     </row>
     <row r="18">
@@ -937,35 +937,35 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>53945000</v>
+        <v>5232000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1209 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №1181 за поставленный товар</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>97216000</v>
+        <v>48168000</v>
       </c>
     </row>
     <row r="19">
@@ -977,35 +977,35 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>12661000</v>
+        <v>4096000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Bekobod Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>319205790</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000044904041001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2932 13.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>109877000</v>
+        <v>52264000</v>
       </c>
     </row>
     <row r="20">
@@ -1015,37 +1015,37 @@
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>11766000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>6048000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Sharq Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>399800755</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000974077314001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4728 за поставленный товар</t>
+          <t>Оплата за сырье по договору №156/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>121643000</v>
+        <v>46216000</v>
       </c>
     </row>
     <row r="21">
@@ -1056,36 +1056,36 @@
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>12438000</v>
+        <v>29915000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплаа за товары согласно счет-фактуре №7485</t>
+          <t>Предоплата за материалы по договору №144/26</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>109205000</v>
+        <v>16301000</v>
       </c>
     </row>
     <row r="22">
@@ -1096,36 +1096,36 @@
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1750000</v>
+        <v>10544000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ilhom Agro MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>229622927</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000779547599001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №84/26</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>107455000</v>
+        <v>5757000</v>
       </c>
     </row>
     <row r="23">
@@ -1136,62 +1136,57 @@
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1750000</v>
+        <v>15700000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6720)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000210409560417</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>Kredit shartnomasi L-2024-6720 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>105705000</v>
+        <v>-9943000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>11667000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>4098000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1201,606 +1196,611 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №81/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №289/26, QQS 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>94038000</v>
+        <v>-5845000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>15700000</v>
+        <v>1750000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6720)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16307000210409560417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6720 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>78338000</v>
+        <v>-7595000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>23922000</v>
+        <v>1750000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2690</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>54416000</v>
+        <v>-9345000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>6090000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>1647000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>310787834</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000924864492001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №13/26</t>
+          <t>Оплата за продукцию по договору №251/26, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>48326000</v>
+        <v>-7698000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>21137000</v>
+        <v>30045000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №224/26 от 17.07.2026</t>
+          <t>Оплата за продукцию по договору №159/26, НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>69463000</v>
+        <v>22347000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>11240000</v>
+        <v>6250000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №178/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №144/26, QQS 12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>80703000</v>
+        <v>28597000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>7813000</v>
+        <v>3513000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8124 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №51/26, НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>88516000</v>
+        <v>32110000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4300000</v>
+        <v>4538000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3886</t>
+          <t>Xom ashyo uchun to'lov, shartn. №197/26, QQS bilan</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>84216000</v>
+        <v>27572000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>7806000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>28409000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo MChJ</t>
+          <t>Oydin Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>236416466</t>
+          <t>200380361</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000860101522001</t>
+          <t>20208000287876351001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №36/26</t>
+          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>76410000</v>
+        <v>55981000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>9637000</v>
+        <v>22508000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shodlik Yog'och MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>300296229</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000767795475001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №69/26 от 20.07.2026</t>
+          <t>Оплата за продукцию по договору №107/26, НДС 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>86047000</v>
+        <v>78489000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>6644000</v>
+        <v>2072000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Angren Avto Savdo AJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>213275725</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000815346809001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №174/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №258/26 от 22.07.2026</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>92691000</v>
+        <v>80561000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3809000</v>
+        <v>18521000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №269/26</t>
+          <t>Предоплата за материалы по договору №173/26</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>88882000</v>
+        <v>62040000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>30214000</v>
+        <v>2998000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6395</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>58668000</v>
+        <v>59042000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>39011000</v>
+        <v>7908000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №228/26</t>
+          <t>Предоплата за материалы по договору №239/26</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>19657000</v>
+        <v>51134000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>18843000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>9506000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №52/26</t>
+          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>814000</v>
+        <v>60640000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3004000</v>
+        <v>1143000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000034879345001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>-2190000</v>
+        <v>59497000</v>
       </c>
     </row>
     <row r="40">
@@ -1810,37 +1810,37 @@
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>15683000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>19746000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Sharq Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>399800755</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000974077314001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №42/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3744</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13493000</v>
+        <v>39751000</v>
       </c>
     </row>
     <row r="41">
@@ -1850,23 +1850,23 @@
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>13994000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>47973000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1876,237 +1876,232 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5574 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5883</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>27487000</v>
+        <v>-8222000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>10180000</v>
+        <v>69554000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №299/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №62/26 от 28.07.2026</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37667000</v>
+        <v>61332000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>6049000</v>
+        <v>2806000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3282</t>
+          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>43716000</v>
+        <v>64138000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1143000</v>
+        <v>14506000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000758574362001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товары согласно счет-фактуре №9194</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>42573000</v>
+        <v>49632000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>3992000</v>
+        <v>12207000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товары согласн счет-фактуре №7916</t>
+          <t>Оплата за сырье по договору №101/26 от 30.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>38581000</v>
+        <v>37425000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>12489000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>2529000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>310787834</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000924864492001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №231/26</t>
+          <t>Оплата по счет-фактуре №2688 за поставленный товар</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>26092000</v>
+        <v>39954000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>5792000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>335107634</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2116,37 +2111,37 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1678 от 28.07.2026, в т.ч. НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>31884000</v>
+        <v>39654000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>3986000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>9056000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2156,37 +2151,37 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №73/26 от 29.07.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №35/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>27898000</v>
+        <v>48710000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>2859000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>7983000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2196,86 +2191,91 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №227/26</t>
+          <t>Оплата за товар по с/ф №1179 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25039000</v>
+        <v>56693000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>18733000</v>
+        <v>5006000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3336 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №9794 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>43772000</v>
+        <v>61699000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>3869000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Oqtosh Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>43472000</v>
+        <v>65568000</v>
       </c>
     </row>
     <row r="52">
@@ -2285,37 +2285,37 @@
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>8824000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>3939000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Angren Avto Savdo AJ</t>
+          <t>Denov Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>213275725</t>
+          <t>303328616</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000815346809001</t>
+          <t>20208000860386260001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №267/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №41/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>52296000</v>
+        <v>61629000</v>
       </c>
     </row>
     <row r="53">
@@ -2326,62 +2326,62 @@
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>8291000</v>
+        <v>4410000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №848</t>
+          <t>Оплата за товары согласно с/ф №7454</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>44005000</v>
+        <v>57219000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>10712000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>4703000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2391,51 +2391,51 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №918 за поставленный товар</t>
+          <t>Оплата за сырье по договору №9/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>54717000</v>
+        <v>52516000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>8238000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>18681000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angren Avto Savdo AJ</t>
+          <t>Ilhom Agro MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>213275725</t>
+          <t>229622927</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000815346809001</t>
+          <t>20208000779547599001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7677 04.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №30/26</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>62955000</v>
+        <v>33835000</v>
       </c>
     </row>
     <row r="56">
@@ -2445,32 +2445,37 @@
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>12619000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>2908000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №2384</t>
+          <t>Оплата по счет-фактуре №8867 за поставленный товар</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>50336000</v>
+        <v>36743000</v>
       </c>
     </row>
     <row r="57">
@@ -2481,116 +2486,111 @@
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>27888000</v>
+        <v>12619000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>236416466</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000860101522001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1076</t>
+          <t>Заработная плата за июль 2026 . (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>22448000</v>
+        <v>24124000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>3327000</v>
+        <v>4847000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bunyodkor Agro MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>268478422</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000356379989001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №42/26 от 06.08.2026</t>
+          <t>Оплата по счет-фактуре №6727 за поставленный товар</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>25775000</v>
+        <v>28971000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>11552000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>2413000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zafar Qurilish MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>397782463</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000366207568001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №211/26</t>
+          <t>Оплата по счет-фактуре №2297 за поставленный товар</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14223000</v>
+        <v>31384000</v>
       </c>
     </row>
     <row r="60">
@@ -2602,61 +2602,61 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>14542000</v>
+        <v>1670000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bunyodkor Mehmonxona AJ</t>
+          <t>Oydin Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>265033286</t>
+          <t>200380361</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000668603862001</t>
+          <t>20208000287876351001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6006 за поставленный товар</t>
+          <t>Tovar uchun to'lov, h/f №8830 07.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>28765000</v>
+        <v>33054000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>11184000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>8231000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2666,51 +2666,51 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №179/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №161/26</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>39949000</v>
+        <v>24823000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>5611000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>17491000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9472 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №262/26</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>45560000</v>
+        <v>7332000</v>
       </c>
     </row>
     <row r="63">
@@ -2720,23 +2720,23 @@
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>1797000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>12556000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>241477296</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000275361176001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2746,77 +2746,77 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №90/21</t>
+          <t>Оплата за продукцию по договору №3/26, НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>43763000</v>
+        <v>19888000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>10057000</v>
+        <v>4662000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №4857 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата по счет-фактуре №1871 за поставленный товар</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>53820000</v>
+        <v>24550000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>6080000</v>
+        <v>4306000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bunyodkor Mehmonxona AJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>265033286</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000668603862001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2826,157 +2826,157 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №51/26 от 12.08.2026</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №257/26, НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>59900000</v>
+        <v>28856000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>8955000</v>
+        <v>1629000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №71/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №5542 за поставленный товар</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>68855000</v>
+        <v>30485000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>4164000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>1797000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Bog'ishamol Qurilish AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>377824637</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000662075680001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №40/26, НДС 12%</t>
+          <t>Аренда помещения за август, дог. №65/20</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>73019000</v>
+        <v>28688000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>3513000</v>
+        <v>4522000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №259/26</t>
+          <t>Оплата за товары согласно счет-фактуре №1210</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>69506000</v>
+        <v>24166000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>29786000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>5063000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2986,112 +2986,117 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №138/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №26/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>39720000</v>
+        <v>29229000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>15700000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>1837000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6720)</t>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>16307000210409560417</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6720 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за продукцию по договору №57/26, НДС 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>24020000</v>
+        <v>31066000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>28069000</v>
+        <v>2033000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Shartnoma №163/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №121 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>52089000</v>
+        <v>33099000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>8668000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>5003000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3101,37 +3106,37 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9094 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №9894</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>60757000</v>
+        <v>28096000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>4353000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>7703000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3141,136 +3146,136 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Shartnoma №213/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №135/26</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>65110000</v>
+        <v>20393000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>4179000</v>
+        <v>2521000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №58/26 от 17.08.2026</t>
+          <t>Оплата по с/ф №462 за поставленный товар</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>69289000</v>
+        <v>22914000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>3530000</v>
+        <v>1845000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>347842203</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000637998941001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №21/26, НДС 12%</t>
+          <t>Оплата по с/ф №1039 за поставленный товар</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>72819000</v>
+        <v>24759000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>3368000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>1721000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4835 за поставленный товар</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>76187000</v>
+        <v>23038000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
@@ -3301,51 +3306,46 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>74466000</v>
+        <v>21317000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46251</v>
+        <v>46249</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>1721000</v>
+        <v>15700000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6720)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000210409560417</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮЛЬ 2026 Г.</t>
+          <t>Kredit shartnomasi L-2024-6720 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>72745000</v>
+        <v>5617000</v>
       </c>
     </row>
     <row r="79">
@@ -3355,23 +3355,23 @@
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>7031000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>26994000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,11 +3381,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №254/26 от 17.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №2414 за поставленный товар</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>65714000</v>
+        <v>32611000</v>
       </c>
     </row>
     <row r="80">
@@ -3395,23 +3395,23 @@
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>79998000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>21735000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3421,77 +3421,77 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6283</t>
+          <t>Оплата по счет-фактуре №9299 за поставленный товар</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-14284000</v>
+        <v>54346000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>16620000</v>
+        <v>1623000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №108/26, QQS 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №268/26 ОТ 17.08.2026</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2336000</v>
+        <v>55969000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>10142000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>4015000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3501,77 +3501,77 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №22/26 от 19.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №496</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>12478000</v>
+        <v>51954000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>12281000</v>
+        <v>10657000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6638</t>
+          <t>Оплата за товары согласно с/ф №546</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>197000</v>
+        <v>41297000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>4828000</v>
+        <v>5424000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>310787834</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000924864492001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3581,37 +3581,37 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №202/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №55/26, НДС 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5025000</v>
+        <v>46721000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>2293000</v>
+        <v>1904000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>310787834</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000924864492001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3621,197 +3621,197 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3035 за поставленный товар</t>
+          <t>Предоплата за товар по договору №115/26 от 18.08.2026</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>7318000</v>
+        <v>48625000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>2931000</v>
+        <v>4313000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Tovarlar uchun to'lov h/f №6043</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>4387000</v>
+        <v>44312000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>6402000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>37734000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Guliston Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>354568603</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000671803885001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №8611</t>
+          <t>Оплата по счет-фактуре №4995 за поставленный товар</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>-2015000</v>
+        <v>82046000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>12906000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>2203000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Shodlik Yog'och MChJ</t>
+          <t>Sharq Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>300296229</t>
+          <t>399800755</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000767795475001</t>
+          <t>20208000974077314001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №185/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №206/26 от 21.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>10891000</v>
+        <v>79843000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>5008000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>19478000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bunyodkor Mehmonxona AJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>265033286</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000668603862001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №727 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №195/26</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>15899000</v>
+        <v>60365000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>1123000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>2005000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Shahrisabz Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>227572578</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000758574362001</t>
+          <t>20208000534680922001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3821,117 +3821,117 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за продукцию по дог. №153/26, НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>14776000</v>
+        <v>62370000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>2310000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>1123000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bunyodkor Mehmonxona AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>265033286</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000668603862001</t>
+          <t>20208000034879345001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1269 за поставленный товар</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>17086000</v>
+        <v>61247000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>5460000</v>
+        <v>3016000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №238/26</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>11626000</v>
+        <v>58231000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46262</v>
+        <v>46258</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>19012000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>3424000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3941,512 +3941,517 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №2/26 от 28.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №279</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>30638000</v>
+        <v>54807000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46262</v>
+        <v>46258</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>3213000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>7245000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Ilhom Agro MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>229622927</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000779547599001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7344 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №7701</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>33851000</v>
+        <v>47562000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>20651000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>7786000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Sharq Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>399800755</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000974077314001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2056 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №29/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>54502000</v>
+        <v>39776000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>3433000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>17377000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Barakali Polimer AJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>356192057</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000050449040001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №8/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №197/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>57935000</v>
+        <v>22399000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>300000</v>
+        <v>50181000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Оплата за транспортные услуги по договору №297/26</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>57635000</v>
+        <v>-27782000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>7976000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>9101000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>236416466</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000860101522001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №986</t>
+          <t>Предоплата за товар по договору №119/26 от 25.08.2026</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>49659000</v>
+        <v>-18681000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>8286000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>7021000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №530</t>
+          <t>Оплата за продукцию по договору №100/26, НДС 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>41373000</v>
+        <v>-11660000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46266</v>
+        <v>46260</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>6144000</v>
+        <v>5196000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2256</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №18/26</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>35229000</v>
+        <v>-16856000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>7673000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>2903000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>236416466</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000860101522001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6010</t>
+          <t>Оплата по с/ф №7644 за поставленный товар</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>27556000</v>
+        <v>-13953000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>3290000</v>
+        <v>2757000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №10/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №147/26, НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>30846000</v>
+        <v>-11196000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46268</v>
+        <v>46262</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>14816000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>236416466</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000860101522001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4976</t>
+          <t>Оплата за продукцию по договору №78/26, НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>25346000</v>
+        <v>3620000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46269</v>
+        <v>46262</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>3911000</v>
+        <v>6620000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6528 04.09.2026, QQS bilan</t>
+          <t>ОПЛАТА ПО С/Ф №6511 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>29257000</v>
+        <v>10240000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>4082000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>5201000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Bekobod Logistik AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>224344093</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000772008791001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №123/26 от 07.09.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №2825</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>33339000</v>
+        <v>5039000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>2665000</v>
+        <v>20404000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Oydin Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>200380361</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000287876351001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4456,272 +4461,272 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №5471</t>
+          <t>Оплата за товар по счет-фактуре №5504 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>36004000</v>
+        <v>25443000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>1835000</v>
+        <v>5192000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>207107878</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000489248644001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактре №9419 за поставленный товар</t>
+          <t>Оплата за прдукцию по договору №152/26, НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>37839000</v>
+        <v>30635000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>4484000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>4600000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №136/26 от 07.09.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №171/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>33355000</v>
+        <v>35235000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>8212000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>4048000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>236416466</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000860101522001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №270/26</t>
+          <t>Оплата по счет-фактуре №9711 за поставленный товар</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>25143000</v>
+        <v>39283000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>13145000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>2215000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №4860</t>
+          <t>Оплата за продукцию по договору №132/26, НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>11998000</v>
+        <v>41498000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>15499000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>248352656</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8613 за поставленный товар</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>27497000</v>
+        <v>41198000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>5332000</v>
+        <v>2275000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Angren Avto Savdo AJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>213275725</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000815346809001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №237/26 от 09.09.2026</t>
+          <t>Shartnoma №76/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>32829000</v>
+        <v>43473000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>1872000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>5899000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>241477296</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000275361176001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4731,37 +4736,37 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №90/21</t>
+          <t>Оплата за товар по с/ф №1827 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>30957000</v>
+        <v>49372000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>7728000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>1762000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4771,37 +4776,37 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №198/26</t>
+          <t>Предоплата за товар по договору №241/26 от 02.09.2026</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>23229000</v>
+        <v>51134000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>4321000</v>
+        <v>1413000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Oydin Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>200380361</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000287876351001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4811,77 +4816,77 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №277/26 от 10.09.2026</t>
+          <t>Оплата за продукцию по договору №112/26, НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>27550000</v>
+        <v>52547000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>24390000</v>
+        <v>43454000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och MChJ</t>
+          <t>Bog'ishamol Poligraf MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>207107878</t>
+          <t>310787834</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000489248644001</t>
+          <t>20208000924864492001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2468 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9844 03.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>51940000</v>
+        <v>96001000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>7263000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>6628000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4891,117 +4896,117 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №14/26</t>
+          <t>Оплата по с/ф №8829 за поставленный товар</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>44677000</v>
+        <v>102629000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>32116000</v>
+        <v>4319000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Guliston Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>354568603</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000671803885001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6307 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №187/26, НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>76793000</v>
+        <v>106948000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>9228000</v>
+        <v>1743000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Shahrisabz Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>227572578</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000534680922001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5620 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №2958 за поставленный товар</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>86021000</v>
+        <v>108691000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>5799000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>3387000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5011,37 +5016,37 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3846 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №70/26</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>91820000</v>
+        <v>105304000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>5087000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>8843000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Sharq Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>233003803</t>
+          <t>399800755</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000182878763001</t>
+          <t>20208000974077314001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5051,632 +5056,632 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №57/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №1434</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>96907000</v>
+        <v>96461000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>2308000</v>
+        <v>3883000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Shahrisabz Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>227572578</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000534680922001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7331 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №230/26, НДС 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>99215000</v>
+        <v>100344000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>1792000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>1805000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Оплата за товар по счет-фактуре №7503 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>97423000</v>
+        <v>102149000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>1792000</v>
+        <v>1362000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №1881</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>95631000</v>
+        <v>100787000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>18597000</v>
+        <v>13145000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>324881016</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №4/26 от 14.09.2026, НДС 12%</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>77034000</v>
+        <v>87642000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>39531000</v>
+        <v>21124000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shodlik Tekstil MChJ</t>
+          <t>Ilhom Agro MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>287934536</t>
+          <t>229622927</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000960113653001</t>
+          <t>20208000779547599001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3578</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №273/26, QQS bilan</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>37503000</v>
+        <v>66518000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>15700000</v>
+        <v>24093000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6720)</t>
+          <t>Qo'qon Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>16307000210409560417</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6720 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Предоплата за материалы по договору №206/26</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>21803000</v>
+        <v>42425000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46281</v>
+        <v>46273</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>2607000</v>
+        <v>4012000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №225/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>24410000</v>
+        <v>46437000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46281</v>
+        <v>46273</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>25146000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>3008000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4409</t>
+          <t>Оплата за продукцию по договору №24/26, НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>-736000</v>
+        <v>49445000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46283</v>
+        <v>46273</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>2117000</v>
+        <v>2052000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №95/26 от 18.09.2026</t>
+          <t>Оплата за продукцию по договору №27/26, НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1381000</v>
+        <v>51497000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>3789000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>5954000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Omad Tur Servis AJ</t>
+          <t>Bekobod Logistik AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>240886110</t>
+          <t>224344093</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000587264826001</t>
+          <t>20208000772008791001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2355 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №202/26</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>5170000</v>
+        <v>45543000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>2978000</v>
+        <v>16937000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kamalak Metall XK</t>
+          <t>Shahrisabz Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>267545686</t>
+          <t>227572578</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000376718038001</t>
+          <t>20208000534680922001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №241/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №164/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>8148000</v>
+        <v>62480000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>6767000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>2979000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zafar Qurilish MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>397782463</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000366207568001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №286/26</t>
+          <t>Предоплата за товар по договору №6/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1381000</v>
+        <v>65459000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>14118000</v>
+        <v>1872000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Bog'ishamol Qurilish AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>377824637</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000662075680001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №188/26</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>-12737000</v>
+        <v>63587000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46287</v>
+        <v>46275</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>7675000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>125532000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Nurafshon Avto Savdo MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>335107634</t>
+          <t>288611025</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000186566824001</t>
+          <t>20208000726482671001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2356 за поставленный товар</t>
+          <t>Оплата за сырье по договору №98/26 от 10.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>-5062000</v>
+        <v>-61945000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46287</v>
+        <v>46276</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>3147000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>1261000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Предоплата за товар по договору №151/26 от 11.09.2026</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>-8209000</v>
+        <v>-60684000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46287</v>
+        <v>46279</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>9353000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>7024000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5686,117 +5691,117 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №64/26 от 22.09.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №230/26, QQS 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>-17562000</v>
+        <v>-53660000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46287</v>
+        <v>46279</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>26477000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>3431000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bunyodkor Farm Savdo MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>236416466</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000860101522001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №12/26</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №100/26 ОТ 14.09.2026</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>-44039000</v>
+        <v>-50229000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46288</v>
+        <v>46279</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>9773000</v>
+        <v>1886000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Angren Avto Savdo AJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>213275725</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000815346809001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8850 23.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №30/26, НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>-34266000</v>
+        <v>-48343000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>15283000</v>
+        <v>1490000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Angren Avto Savdo AJ</t>
+          <t>Oydin Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>213275725</t>
+          <t>200380361</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000815346809001</t>
+          <t>20208000287876351001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5806,37 +5811,37 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3220 24.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №1733 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>-18983000</v>
+        <v>-46853000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>21940000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>1200000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5846,77 +5851,72 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №117/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №95/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>-40923000</v>
+        <v>-45653000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46290</v>
+        <v>46280</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>3094000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>248352656</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6720)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>16307000210409560417</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Shartnoma №12/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2024-6720 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>-37829000</v>
+        <v>-61353000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46290</v>
+        <v>46281</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>2717000</v>
+        <v>14639000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bunyodkor Mehmonxona AJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>265033286</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000668603862001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5926,277 +5926,277 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2272 от 25.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №391 от 16.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>-35112000</v>
+        <v>-46714000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>12903000</v>
+        <v>2145000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №703 28.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №250/26 от 16.09.2026</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>-22209000</v>
+        <v>-44569000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>8234000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>1792000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3955 за поставленный товар</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>-13975000</v>
+        <v>-46361000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>5148000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>1792000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №14 за поставленный товар</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>-8827000</v>
+        <v>-48153000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>4126000</v>
+        <v>5527000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4349 ОТ 28.09.2026, В Т.Ч. НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7355 17.09.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>-4701000</v>
+        <v>-42626000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>3367000</v>
+        <v>1217000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №5397 ОТ 28.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №101/26 от 17.09.2026</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>-1334000</v>
+        <v>-41409000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46293</v>
+        <v>46283</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1170000</v>
+        <v>2392000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ziyo Tekstil MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>341646638</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000758574362001</t>
+          <t>20208000010152233001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товары согласно счет-фактуре №3618</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>-2504000</v>
+        <v>-43801000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>7235000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>29156000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>324881016</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000207861141001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6206,37 +6206,37 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №284/26</t>
+          <t>Предоплата за товар по дог. №88/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>-9739000</v>
+        <v>-14645000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>17333000</v>
+        <v>17791000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kamalak Metall XK</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>267545686</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000376718038001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6246,231 +6246,871 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7534 от 29.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №9782 за поставленный товар</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>7594000</v>
+        <v>3146000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>15339000</v>
+        <v>6273000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8547 ОТ 29.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9869 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>22933000</v>
+        <v>9419000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>2240000</v>
+        <v>4987000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Zarafshon Non MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>335265663</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>20208000916684660001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2764 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7854</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>25173000</v>
+        <v>14406000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>21785000</v>
+        <v>4161000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Angren Avto Savdo AJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>213275725</t>
+          <t>310763451</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000815346809001</t>
+          <t>20208000656682469001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2096 от 30.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №37/26, НДС 12%</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46958000</v>
+        <v>18567000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>1842000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>3190000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tong Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>248352656</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000309166846001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №210/26 ОТ 30.09.2026</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>48800000</v>
+        <v>15377000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n">
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>9326000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Guliston Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>354568603</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000671803885001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №6309 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>24703000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>6409000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>335265663</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000916684660001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №47/26 от 22.09.2026</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>31112000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>2280000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>335265663</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000916684660001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №1472 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>33392000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>2157000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Oqtosh Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>310763451</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000656682469001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №376 от 2209.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>35549000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>8817000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Qo'qon Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>288611025</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000726482671001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №9386</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>26732000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>3164000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Shahrisabz Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>227572578</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000534680922001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №216/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>29896000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>1311000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Oydin Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>200380361</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000287876351001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №1891 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>31207000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>1109000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Oqtosh Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>310763451</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000656682469001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1778 ОТ 24.09.2026, В Т.Ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>32316000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>26484000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>335265663</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000916684660001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №24/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>58800000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>1493000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>335265663</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000916684660001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №256/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>60293000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>3358000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>335265663</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000916684660001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №9252 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>63651000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>1544000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Zarafshon Non MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>335265663</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000916684660001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4779</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>65195000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>1392000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Shahrisabz Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>227572578</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000534680922001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №6291 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>66587000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000034879345001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>65417000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>1459000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Bog'ishamol Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>310787834</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000924864492001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №497 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>66876000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>18076000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Qo'qon Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>288611025</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000726482671001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №163/26 от 29.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>48800000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" t="inlineStr">
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" t="inlineStr">
         <is>
           <t>Bodomzor Bank ATB</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>01204</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
         <v>48500000</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n">
-        <v>753114000</v>
-      </c>
-      <c r="D157" s="4" t="n">
-        <v>756814000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="C173" s="4" t="n">
+        <v>763314000</v>
+      </c>
+      <c r="D173" s="4" t="n">
+        <v>767014000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C158" s="4" t="n">
+      <c r="C174" s="4" t="n">
         <v>48500000</v>
       </c>
-      <c r="D158" s="4" t="n"/>
+      <c r="D174" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
